--- a/task-reviews/graph/task_graph_counting_degree_count/task_graph_counting_degree_count.xlsx
+++ b/task-reviews/graph/task_graph_counting_degree_count/task_graph_counting_degree_count.xlsx
@@ -156,9 +156,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -184,9 +181,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -212,9 +206,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -240,9 +231,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -268,9 +256,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -296,9 +281,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -324,9 +306,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -352,9 +331,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -380,9 +356,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -408,9 +381,1006 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="48" name="Image 48" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId48"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="49" name="Image 49" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId49"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="50" name="Image 50" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId50"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -441,9 +1411,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -469,9 +1436,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -497,9 +1461,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -525,9 +1486,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -553,9 +1511,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -581,9 +1536,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -609,9 +1561,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -637,9 +1586,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -665,9 +1611,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -693,9 +1636,1006 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="48" name="Image 48" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId48"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="49" name="Image 49" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId49"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="50" name="Image 50" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId50"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -726,9 +2666,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -754,9 +2691,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -782,9 +2716,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -810,9 +2741,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -838,9 +2766,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -866,9 +2791,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -894,9 +2816,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -922,9 +2841,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -950,9 +2866,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -978,9 +2891,1006 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="48" name="Image 48" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId48"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="49" name="Image 49" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId49"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3657600" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="50" name="Image 50" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId50"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1277,7 +4187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -1375,31 +4285,31 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Look at the image with a labeled undirected graph. Question: How many nodes have degree 1?
+          <t>Work from the image with a labeled undirected graph. Answer this question: How many nodes have degree 0?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value, sorted in ascending label order.
-Answer field: set "answer" to the count of matching nodes as an integer.
+Evidence format: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer requirement: set "answer" to the count of matching nodes as an integer.
 Example JSON:
 {"evidence":["B","F"],"answer":2}</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Look at the image with a labeled undirected graph. Question: How many nodes have degree 1?
+          <t>Work from the image with a labeled undirected graph. Answer this question: How many nodes have degree 0?
 Return a valid JSON object with key "answer".
-Answer field: set "answer" to the count of matching nodes as an integer.
+Answer requirement: set "answer" to the count of matching nodes as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["F", "I", "J"], "answer": 3}</t>
+          <t>{"evidence": ["C"], "answer": 1}</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>["F", "I", "J"]</t>
+          <t>["C"]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1413,16 +4323,16 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2548615245070299</v>
+        <v>127835601484259</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_counting_degree_count/images/degree_count/0003.png</t>
+          <t>graph/task_graph_counting_degree_count/images/degree_count/0002.png</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_counting_degree_count/data/degree_count/0003.json</t>
+          <t>graph/task_graph_counting_degree_count/data/degree_count/0002.json</t>
         </is>
       </c>
     </row>
@@ -1439,31 +4349,31 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Look at the image with a labeled undirected graph. Determine the answer: How many nodes have degree 1?
+          <t>Look at the image with a labeled undirected graph. Answer this question: How many nodes have degree 4?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value, sorted in ascending label order.
-Answer rule: set "answer" to the count of matching nodes as an integer.
+Evidence: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer: set "answer" to the count of matching nodes as an integer.
 Example JSON:
 {"evidence":["B","F"],"answer":2}</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Look at the image with a labeled undirected graph. Determine the answer: How many nodes have degree 1?
+          <t>Look at the image with a labeled undirected graph. Answer this question: How many nodes have degree 4?
 Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the count of matching nodes as an integer.
+Answer: set "answer" to the count of matching nodes as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["1", "2", "5", "6", "9"], "answer": 5}</t>
+          <t>{"evidence": ["A"], "answer": 1}</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>["1", "2", "5", "6", "9"]</t>
+          <t>["A"]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1477,16 +4387,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>4099619367864645</v>
+        <v>137439306934389</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_counting_degree_count/images/degree_count/0001.png</t>
+          <t>graph/task_graph_counting_degree_count/images/degree_count/0022.png</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_counting_degree_count/data/degree_count/0001.json</t>
+          <t>graph/task_graph_counting_degree_count/data/degree_count/0022.json</t>
         </is>
       </c>
     </row>
@@ -1503,31 +4413,31 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Work from the image with a labeled undirected graph. How many nodes have degree 4?
+          <t>You are given an image with a labeled undirected graph. Determine the answer: How many nodes have degree 1?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value, sorted in ascending label order.
-Answer format: set "answer" to the count of matching nodes as an integer.
-Example JSON:
-{"evidence":["B","F"],"answer":2}</t>
+Evidence format: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer requirement: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Work from the image with a labeled undirected graph. How many nodes have degree 4?
+          <t>You are given an image with a labeled undirected graph. Determine the answer: How many nodes have degree 1?
 Return a valid JSON object with key "answer".
-Answer format: set "answer" to the count of matching nodes as an integer.
+Answer rule: set "answer" to the count of matching nodes as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["E", "F", "G"], "answer": 3}</t>
+          <t>{"evidence": ["2", "3", "4", "5", "6"], "answer": 5}</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>["E", "F", "G"]</t>
+          <t>["2", "3", "4", "5", "6"]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1541,16 +4451,16 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4103609622165697</v>
+        <v>232988897626177</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_counting_degree_count/images/degree_count/0004.png</t>
+          <t>graph/task_graph_counting_degree_count/images/degree_count/0023.png</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_counting_degree_count/data/degree_count/0004.json</t>
+          <t>graph/task_graph_counting_degree_count/data/degree_count/0023.json</t>
         </is>
       </c>
     </row>
@@ -1567,31 +4477,31 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Use the image containing a labeled undirected graph. Task: How many nodes have degree 4?
+          <t>Look at the image with a labeled undirected graph. Answer this question: How many nodes have degree 3?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value, sorted in ascending label order.
-Answer requirement: set "answer" to the count of matching nodes as an integer.
+Evidence rule: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer rule: set "answer" to the count of matching nodes as an integer.
 Example JSON:
 {"evidence":["B","F"],"answer":2}</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Use the image containing a labeled undirected graph. Task: How many nodes have degree 4?
+          <t>Look at the image with a labeled undirected graph. Answer this question: How many nodes have degree 3?
 Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the count of matching nodes as an integer.
+Answer format: set "answer" to the count of matching nodes as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["1", "2", "4", "7"], "answer": 4}</t>
+          <t>{"evidence": ["A", "C", "D", "E", "G"], "answer": 5}</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>["1", "2", "4", "7"]</t>
+          <t>["A", "C", "D", "E", "G"]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1605,16 +4515,16 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>5895631438541725</v>
+        <v>641328944179895</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_counting_degree_count/images/degree_count/0000.png</t>
+          <t>graph/task_graph_counting_degree_count/images/degree_count/0010.png</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_counting_degree_count/data/degree_count/0000.json</t>
+          <t>graph/task_graph_counting_degree_count/data/degree_count/0010.json</t>
         </is>
       </c>
     </row>
@@ -1631,54 +4541,1334 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled undirected graph. Determine the answer: How many nodes have degree 2?
+          <t>Work from the image with a labeled undirected graph. Task: How many nodes have degree 0?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value, sorted in ascending label order.
+Evidence requirement: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer format: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["B","F"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Work from the image with a labeled undirected graph. Task: How many nodes have degree 0?
+Return a valid JSON object with key "answer".
 Answer field: set "answer" to the count of matching nodes as an integer.
 Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["A", "B", "E", "H"], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>["A", "B", "E", "H"]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1073697871631726</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/degree_count/0015.png</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/degree_count/0015.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="213.75" customHeight="1">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>degree_count</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled undirected graph. Determine the answer: How many nodes have degree 2?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer rule: set "answer" to the count of matching nodes as an integer.
+Example JSON:
 {"evidence":["B","F"],"answer":2}</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>You are given an image with a labeled undirected graph. Determine the answer: How many nodes have degree 2?
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled undirected graph. Determine the answer: How many nodes have degree 2?
 Return a valid JSON object with key "answer".
 Answer requirement: set "answer" to the count of matching nodes as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["B", "C", "D", "E", "F"], "answer": 5}</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>["B", "C", "D", "E", "F"]</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["A", "B", "C", "F", "I"], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>["A", "B", "C", "F", "I"]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>label_set</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>8233787990375358</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>graph/task_graph_counting_degree_count/images/degree_count/0002.png</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>graph/task_graph_counting_degree_count/data/degree_count/0002.json</t>
+      <c r="K7" t="n">
+        <v>1282529125672466</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/degree_count/0016.png</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/degree_count/0016.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="213.75" customHeight="1">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>degree_count</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled undirected graph. Task: How many nodes have degree 2?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer requirement: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["B","F"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled undirected graph. Task: How many nodes have degree 2?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["C", "F", "G", "H", "J"], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>["C", "F", "G", "H", "J"]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1472311588082666</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/degree_count/0024.png</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/degree_count/0024.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="213.75" customHeight="1">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>degree_count</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Use the image containing a labeled undirected graph. Answer this question: How many nodes have degree 4?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer field: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Use the image containing a labeled undirected graph. Answer this question: How many nodes have degree 4?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["5", "6", "9"], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>["5", "6", "9"]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1777639068923418</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/degree_count/0006.png</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/degree_count/0006.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="213.75" customHeight="1">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>degree_count</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Work from the image with a labeled undirected graph. Determine the answer: How many nodes have degree 3?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer requirement: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["B","F"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Work from the image with a labeled undirected graph. Determine the answer: How many nodes have degree 3?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["C", "E", "F", "G"], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>["C", "E", "F", "G"]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>2037899354017420</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/degree_count/0021.png</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/degree_count/0021.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="213.75" customHeight="1">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>degree_count</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Work from the image with a labeled undirected graph. How many nodes have degree 0?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer field: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Work from the image with a labeled undirected graph. How many nodes have degree 0?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [], "answer": 0}</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>2687428539782697</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/degree_count/0003.png</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/degree_count/0003.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="213.75" customHeight="1">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>degree_count</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with a labeled undirected graph. Question: How many nodes have degree 4?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with a labeled undirected graph. Question: How many nodes have degree 4?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["5", "9"], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>["5", "9"]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>2745519666924849</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/degree_count/0020.png</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/degree_count/0020.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="213.75" customHeight="1">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>degree_count</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled undirected graph. How many nodes have degree 2?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer format: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled undirected graph. How many nodes have degree 2?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["3", "4", "7"], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>["3", "4", "7"]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>4226045081406833</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/degree_count/0001.png</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/degree_count/0001.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="213.75" customHeight="1">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>degree_count</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with a labeled undirected graph. Question: How many nodes have degree 4?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer field: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["B","F"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with a labeled undirected graph. Question: How many nodes have degree 4?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["A", "H"], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>["A", "H"]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>4624906513110308</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/degree_count/0004.png</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/degree_count/0004.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="213.75" customHeight="1">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>degree_count</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Use the image containing a labeled undirected graph. How many nodes have degree 1?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Use the image containing a labeled undirected graph. How many nodes have degree 1?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["1", "4"], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>["1", "4"]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>4738206880462597</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/degree_count/0013.png</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/degree_count/0013.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="213.75" customHeight="1">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>degree_count</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled undirected graph. How many nodes have degree 2?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["B","F"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled undirected graph. How many nodes have degree 2?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["A", "B", "C", "D", "E"], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>["A", "B", "C", "D", "E"]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>4935939549703344</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/degree_count/0012.png</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/degree_count/0012.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="213.75" customHeight="1">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>degree_count</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled undirected graph. Task: How many nodes have degree 2?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer format: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled undirected graph. Task: How many nodes have degree 2?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [], "answer": 0}</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>5492652004742748</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/degree_count/0000.png</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/degree_count/0000.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="213.75" customHeight="1">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>degree_count</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Use the image containing a labeled undirected graph. Question: How many nodes have degree 4?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer rule: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["B","F"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Use the image containing a labeled undirected graph. Question: How many nodes have degree 4?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["B", "C", "D", "H"], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>["B", "C", "D", "H"]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>5565012559655647</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/degree_count/0009.png</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/degree_count/0009.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="213.75" customHeight="1">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>degree_count</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled undirected graph. Question: How many nodes have degree 4?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["B","F"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled undirected graph. Question: How many nodes have degree 4?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [], "answer": 0}</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>5862165747349598</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/degree_count/0018.png</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/degree_count/0018.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="213.75" customHeight="1">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>degree_count</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled undirected graph. Task: How many nodes have degree 1?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer rule: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled undirected graph. Task: How many nodes have degree 1?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["1", "6", "8"], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>["1", "6", "8"]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>5912818488509454</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/degree_count/0005.png</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/degree_count/0005.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="213.75" customHeight="1">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>degree_count</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled undirected graph. How many nodes have degree 4?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer rule: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["B","F"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled undirected graph. How many nodes have degree 4?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["H"], "answer": 1}</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>["H"]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>6315595207916938</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/degree_count/0011.png</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/degree_count/0011.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="213.75" customHeight="1">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>degree_count</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled undirected graph. Task: How many nodes have degree 3?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer requirement: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["B","F"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled undirected graph. Task: How many nodes have degree 3?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["A", "B", "D", "F", "H"], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>["A", "B", "D", "F", "H"]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>8021664639130572</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/degree_count/0007.png</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/degree_count/0007.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="213.75" customHeight="1">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>degree_count</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled undirected graph. How many nodes have degree 4?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled undirected graph. How many nodes have degree 4?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [], "answer": 0}</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>8483950243470879</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/degree_count/0019.png</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/degree_count/0019.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="213.75" customHeight="1">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>degree_count</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled undirected graph. Task: How many nodes have degree 1?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer field: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["B","F"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled undirected graph. Task: How many nodes have degree 1?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["A", "D", "E"], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>["A", "D", "E"]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>8682516582952531</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/degree_count/0008.png</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/degree_count/0008.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="213.75" customHeight="1">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>degree_count</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Work from the image with a labeled undirected graph. How many nodes have degree 3?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer format: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Work from the image with a labeled undirected graph. How many nodes have degree 3?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["1", "2", "3", "7", "9"], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>["1", "2", "3", "7", "9"]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>8731779461849696</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/degree_count/0017.png</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/degree_count/0017.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="213.75" customHeight="1">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>degree_count</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled undirected graph. Task: How many nodes have degree 4?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled undirected graph. Task: How many nodes have degree 4?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["1", "2", "6", "8"], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>["1", "2", "6", "8"]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>8735330145701948</v>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/degree_count/0014.png</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/degree_count/0014.json</t>
         </is>
       </c>
     </row>
@@ -1694,7 +5884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -1792,31 +5982,31 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Work from the image with a labeled directed graph. Answer this question: How many nodes have in-degree 2?
+          <t>Work from the image with a labeled directed graph. Question: How many nodes have in-degree 4?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value, sorted in ascending label order.
-Answer requirement: set "answer" to the count of matching nodes as an integer.
-Example JSON:
-{"evidence":["B","F"],"answer":2}</t>
+Evidence requirement: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer format: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Work from the image with a labeled directed graph. Answer this question: How many nodes have in-degree 2?
+          <t>Work from the image with a labeled directed graph. Question: How many nodes have in-degree 4?
 Return a valid JSON object with key "answer".
-Answer format: set "answer" to the count of matching nodes as an integer.
+Answer rule: set "answer" to the count of matching nodes as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["5", "7"], "answer": 2}</t>
+          <t>{"evidence": ["1", "2", "4"], "answer": 3}</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>["5", "7"]</t>
+          <t>["1", "2", "4"]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1830,16 +6020,16 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>271426421895726</v>
+        <v>311723923409431</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_counting_degree_count/images/in_degree_count/0000.png</t>
+          <t>graph/task_graph_counting_degree_count/images/in_degree_count/0006.png</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_counting_degree_count/data/in_degree_count/0000.json</t>
+          <t>graph/task_graph_counting_degree_count/data/in_degree_count/0006.json</t>
         </is>
       </c>
     </row>
@@ -1856,17 +6046,17 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>The image shows a labeled directed graph. Answer this question: How many nodes have in-degree 4?
+          <t>Use the image containing a labeled directed graph. How many nodes have in-degree 0?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value, sorted in ascending label order.
-Answer: set "answer" to the count of matching nodes as an integer.
+Evidence format: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer requirement: set "answer" to the count of matching nodes as an integer.
 Example JSON:
 {"evidence":["B","F"],"answer":2}</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>The image shows a labeled directed graph. Answer this question: How many nodes have in-degree 4?
+          <t>Use the image containing a labeled directed graph. How many nodes have in-degree 0?
 Return a valid JSON object with key "answer".
 Answer rule: set "answer" to the count of matching nodes as an integer.
 Example JSON:
@@ -1875,12 +6065,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["1", "3", "5"], "answer": 3}</t>
+          <t>{"evidence": ["C", "F", "G"], "answer": 3}</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>["1", "3", "5"]</t>
+          <t>["C", "F", "G"]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1894,16 +6084,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1410570932473064</v>
+        <v>358922951446143</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_counting_degree_count/images/in_degree_count/0004.png</t>
+          <t>graph/task_graph_counting_degree_count/images/in_degree_count/0018.png</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_counting_degree_count/data/in_degree_count/0004.json</t>
+          <t>graph/task_graph_counting_degree_count/data/in_degree_count/0018.json</t>
         </is>
       </c>
     </row>
@@ -1920,31 +6110,31 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled directed graph. Question: How many nodes have in-degree 3?
+          <t>Look at the image with a labeled directed graph. How many nodes have in-degree 1?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value, sorted in ascending label order.
-Answer field: set "answer" to the count of matching nodes as an integer.
-Example JSON:
-{"evidence":["B","F"],"answer":2}</t>
+Evidence format: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer requirement: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled directed graph. Question: How many nodes have in-degree 3?
+          <t>Look at the image with a labeled directed graph. How many nodes have in-degree 1?
 Return a valid JSON object with key "answer".
-Answer format: set "answer" to the count of matching nodes as an integer.
+Answer: set "answer" to the count of matching nodes as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["2", "3", "7"], "answer": 3}</t>
+          <t>{"evidence": [], "answer": 0}</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>["2", "3", "7"]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1958,16 +6148,16 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>2551478491428921</v>
+        <v>610787411052163</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_counting_degree_count/images/in_degree_count/0002.png</t>
+          <t>graph/task_graph_counting_degree_count/images/in_degree_count/0009.png</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_counting_degree_count/data/in_degree_count/0002.json</t>
+          <t>graph/task_graph_counting_degree_count/data/in_degree_count/0009.json</t>
         </is>
       </c>
     </row>
@@ -1984,17 +6174,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Look at the image with a labeled directed graph. Answer this question: How many nodes have in-degree 2?
+          <t>The image shows a labeled directed graph. Task: How many nodes have in-degree 4?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value, sorted in ascending label order.
-Answer: set "answer" to the count of matching nodes as an integer.
-Example JSON:
-{"evidence":["B","F"],"answer":2}</t>
+Evidence format: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer requirement: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Look at the image with a labeled directed graph. Answer this question: How many nodes have in-degree 2?
+          <t>The image shows a labeled directed graph. Task: How many nodes have in-degree 4?
 Return a valid JSON object with key "answer".
 Answer format: set "answer" to the count of matching nodes as an integer.
 Example JSON:
@@ -2003,12 +6193,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": [], "answer": 0}</t>
+          <t>{"evidence": ["2", "7"], "answer": 2}</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["2", "7"]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2022,16 +6212,16 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>4850406808378888</v>
+        <v>750972580760546</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_counting_degree_count/images/in_degree_count/0001.png</t>
+          <t>graph/task_graph_counting_degree_count/images/in_degree_count/0003.png</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_counting_degree_count/data/in_degree_count/0001.json</t>
+          <t>graph/task_graph_counting_degree_count/data/in_degree_count/0003.json</t>
         </is>
       </c>
     </row>
@@ -2048,54 +6238,1334 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Look at the image with a labeled directed graph. Determine the answer: How many nodes have in-degree 3?
+          <t>You are given an image with a labeled directed graph. Question: How many nodes have in-degree 1?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value, sorted in ascending label order.
+Evidence rule: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer rule: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with a labeled directed graph. Question: How many nodes have in-degree 1?
+Return a valid JSON object with key "answer".
 Answer field: set "answer" to the count of matching nodes as an integer.
 Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["1", "3", "4", "5", "6"], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>["1", "3", "4", "5", "6"]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>979927706692573</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/in_degree_count/0020.png</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/in_degree_count/0020.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="213.75" customHeight="1">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>in_degree_count</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled directed graph. Task: How many nodes have in-degree 0?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer format: set "answer" to the count of matching nodes as an integer.
+Example JSON:
 {"evidence":["B","F"],"answer":2}</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Look at the image with a labeled directed graph. Determine the answer: How many nodes have in-degree 3?
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled directed graph. Task: How many nodes have in-degree 0?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [], "answer": 0}</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1502484153374856</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/in_degree_count/0024.png</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/in_degree_count/0024.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="213.75" customHeight="1">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>in_degree_count</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Use the image containing a labeled directed graph. Determine the answer: How many nodes have in-degree 1?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Use the image containing a labeled directed graph. Determine the answer: How many nodes have in-degree 1?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["2", "3", "4", "6"], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>["2", "3", "4", "6"]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>2099113386011739</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/in_degree_count/0022.png</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/in_degree_count/0022.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="213.75" customHeight="1">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>in_degree_count</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled directed graph. Question: How many nodes have in-degree 3?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer field: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["B","F"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled directed graph. Question: How many nodes have in-degree 3?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["A", "D"], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>["A", "D"]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>2100103846034918</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/in_degree_count/0005.png</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/in_degree_count/0005.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="213.75" customHeight="1">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>in_degree_count</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled directed graph. Determine the answer: How many nodes have in-degree 4?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer format: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled directed graph. Determine the answer: How many nodes have in-degree 4?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["1", "2", "6", "7"], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>["1", "2", "6", "7"]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>2152089438434248</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/in_degree_count/0013.png</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/in_degree_count/0013.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="213.75" customHeight="1">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>in_degree_count</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with a labeled directed graph. Question: How many nodes have in-degree 2?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer requirement: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["B","F"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with a labeled directed graph. Question: How many nodes have in-degree 2?
 Return a valid JSON object with key "answer".
 Answer requirement: set "answer" to the count of matching nodes as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["A", "B", "C", "E", "F"], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>["A", "B", "C", "E", "F"]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>2475737112545637</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/in_degree_count/0010.png</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/in_degree_count/0010.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="213.75" customHeight="1">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>in_degree_count</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled directed graph. How many nodes have in-degree 1?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["B","F"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled directed graph. How many nodes have in-degree 1?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["F"], "answer": 1}</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>["F"]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>2670774201456693</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/in_degree_count/0017.png</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/in_degree_count/0017.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="213.75" customHeight="1">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>in_degree_count</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled directed graph. How many nodes have in-degree 0?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer rule: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["B","F"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled directed graph. How many nodes have in-degree 0?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["C", "D", "E"], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>["C", "D", "E"]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>3689229638157503</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/in_degree_count/0019.png</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/in_degree_count/0019.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="213.75" customHeight="1">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>in_degree_count</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Use the image containing a labeled directed graph. How many nodes have in-degree 3?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Use the image containing a labeled directed graph. How many nodes have in-degree 3?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [], "answer": 0}</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>4254878361089650</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/in_degree_count/0008.png</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/in_degree_count/0008.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="213.75" customHeight="1">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>in_degree_count</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Use the image containing a labeled directed graph. Question: How many nodes have in-degree 1?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer requirement: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Use the image containing a labeled directed graph. Question: How many nodes have in-degree 1?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["1", "3", "4", "6", "8"], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>["1", "3", "4", "6", "8"]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>4571677463610599</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/in_degree_count/0001.png</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/in_degree_count/0001.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="213.75" customHeight="1">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>in_degree_count</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled directed graph. Question: How many nodes have in-degree 1?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer format: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled directed graph. Question: How many nodes have in-degree 1?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [], "answer": 0}</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>4848809860753562</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/in_degree_count/0000.png</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/in_degree_count/0000.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="213.75" customHeight="1">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>in_degree_count</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled directed graph. How many nodes have in-degree 1?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer format: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["B","F"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled directed graph. How many nodes have in-degree 1?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [], "answer": 0}</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>4912123273405699</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/in_degree_count/0014.png</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/in_degree_count/0014.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="213.75" customHeight="1">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>in_degree_count</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled directed graph. How many nodes have in-degree 2?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled directed graph. How many nodes have in-degree 2?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["7"], "answer": 1}</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>["7"]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>5053171815844444</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/in_degree_count/0011.png</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/in_degree_count/0011.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="213.75" customHeight="1">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>in_degree_count</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with a labeled directed graph. Question: How many nodes have in-degree 0?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with a labeled directed graph. Question: How many nodes have in-degree 0?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["1", "3"], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>["1", "3"]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>5236910272952306</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/in_degree_count/0021.png</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/in_degree_count/0021.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="213.75" customHeight="1">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>in_degree_count</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with a labeled directed graph. How many nodes have in-degree 1?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer field: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["B","F"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with a labeled directed graph. How many nodes have in-degree 1?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>{"evidence": ["B", "C", "D"], "answer": 3}</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>["B", "C", "D"]</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>label_set</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>6007458828311684</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>graph/task_graph_counting_degree_count/images/in_degree_count/0003.png</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>graph/task_graph_counting_degree_count/data/in_degree_count/0003.json</t>
+      <c r="K20" t="n">
+        <v>7161299117936255</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/in_degree_count/0023.png</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/in_degree_count/0023.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="213.75" customHeight="1">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>in_degree_count</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled directed graph. Answer this question: How many nodes have in-degree 0?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer format: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled directed graph. Answer this question: How many nodes have in-degree 0?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["1", "2", "4", "7"], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>["1", "2", "4", "7"]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>7369195496193441</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/in_degree_count/0015.png</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/in_degree_count/0015.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="213.75" customHeight="1">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>in_degree_count</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled directed graph. How many nodes have in-degree 3?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer rule: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["B","F"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled directed graph. How many nodes have in-degree 3?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["A", "B", "C", "D", "G"], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>["A", "B", "C", "D", "G"]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>7664058392631762</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/in_degree_count/0002.png</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/in_degree_count/0002.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="213.75" customHeight="1">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>in_degree_count</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled directed graph. Task: How many nodes have in-degree 2?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer rule: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled directed graph. Task: How many nodes have in-degree 2?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["5"], "answer": 1}</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>["5"]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>7900691387660938</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/in_degree_count/0004.png</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/in_degree_count/0004.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="213.75" customHeight="1">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>in_degree_count</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Use the image containing a labeled directed graph. Question: How many nodes have in-degree 3?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Use the image containing a labeled directed graph. Question: How many nodes have in-degree 3?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["4", "5", "6"], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>["4", "5", "6"]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>8444351779012982</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/in_degree_count/0016.png</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/in_degree_count/0016.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="213.75" customHeight="1">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>in_degree_count</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled directed graph. Question: How many nodes have in-degree 3?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer field: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled directed graph. Question: How many nodes have in-degree 3?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["1", "2", "9"], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>["1", "2", "9"]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>8502825283318305</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/in_degree_count/0012.png</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/in_degree_count/0012.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="213.75" customHeight="1">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>in_degree_count</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with a labeled directed graph. How many nodes have in-degree 0?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer rule: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["B","F"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with a labeled directed graph. How many nodes have in-degree 0?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["A", "B", "C", "D", "F"], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>["A", "B", "C", "D", "F"]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>8606802613254825</v>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/in_degree_count/0007.png</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/in_degree_count/0007.json</t>
         </is>
       </c>
     </row>
@@ -2111,7 +7581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -2209,31 +7679,31 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>The image shows a labeled directed graph. Task: How many nodes have out-degree 4?
+          <t>Use the image containing a labeled directed graph. Determine the answer: How many nodes have out-degree 1?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value, sorted in ascending label order.
-Answer format: set "answer" to the count of matching nodes as an integer.
+Evidence: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer: set "answer" to the count of matching nodes as an integer.
 Example JSON:
 {"evidence":["B","F"],"answer":2}</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>The image shows a labeled directed graph. Task: How many nodes have out-degree 4?
+          <t>Use the image containing a labeled directed graph. Determine the answer: How many nodes have out-degree 1?
 Return a valid JSON object with key "answer".
-Answer field: set "answer" to the count of matching nodes as an integer.
+Answer requirement: set "answer" to the count of matching nodes as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["7"], "answer": 1}</t>
+          <t>{"evidence": ["A", "D"], "answer": 2}</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>["7"]</t>
+          <t>["A", "D"]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -2247,16 +7717,16 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>7100339559817609</v>
+        <v>887406487958999</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_counting_degree_count/images/out_degree_count/0001.png</t>
+          <t>graph/task_graph_counting_degree_count/images/out_degree_count/0008.png</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_counting_degree_count/data/out_degree_count/0001.json</t>
+          <t>graph/task_graph_counting_degree_count/data/out_degree_count/0008.json</t>
         </is>
       </c>
     </row>
@@ -2273,17 +7743,17 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Look at the image with a labeled directed graph. How many nodes have out-degree 3?
+          <t>You are given an image with a labeled directed graph. Question: How many nodes have out-degree 4?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value, sorted in ascending label order.
-Answer field: set "answer" to the count of matching nodes as an integer.
+Evidence: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer: set "answer" to the count of matching nodes as an integer.
 Example JSON:
 {"evidence":["B","F"],"answer":2}</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Look at the image with a labeled directed graph. How many nodes have out-degree 3?
+          <t>You are given an image with a labeled directed graph. Question: How many nodes have out-degree 4?
 Return a valid JSON object with key "answer".
 Answer format: set "answer" to the count of matching nodes as an integer.
 Example JSON:
@@ -2292,12 +7762,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["B", "D", "E", "G"], "answer": 4}</t>
+          <t>{"evidence": ["A", "B", "F", "G"], "answer": 4}</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>["B", "D", "E", "G"]</t>
+          <t>["A", "B", "F", "G"]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -2311,16 +7781,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>7161451623989232</v>
+        <v>965497186555585</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_counting_degree_count/images/out_degree_count/0003.png</t>
+          <t>graph/task_graph_counting_degree_count/images/out_degree_count/0015.png</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_counting_degree_count/data/out_degree_count/0003.json</t>
+          <t>graph/task_graph_counting_degree_count/data/out_degree_count/0015.json</t>
         </is>
       </c>
     </row>
@@ -2337,31 +7807,31 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled directed graph. Determine the answer: How many nodes have out-degree 2?
+          <t>Work from the image with a labeled directed graph. Determine the answer: How many nodes have out-degree 3?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value, sorted in ascending label order.
+Evidence field: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
 Answer field: set "answer" to the count of matching nodes as an integer.
 Example JSON:
-{"evidence":["B","F"],"answer":2}</t>
+{"evidence":["2","7"],"answer":2}</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>You are given an image with a labeled directed graph. Determine the answer: How many nodes have out-degree 2?
+          <t>Work from the image with a labeled directed graph. Determine the answer: How many nodes have out-degree 3?
 Return a valid JSON object with key "answer".
-Answer format: set "answer" to the count of matching nodes as an integer.
+Answer rule: set "answer" to the count of matching nodes as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["A", "D", "E", "F"], "answer": 4}</t>
+          <t>{"evidence": ["8"], "answer": 1}</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>["A", "D", "E", "F"]</t>
+          <t>["8"]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -2375,16 +7845,16 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>7896709023038310</v>
+        <v>1139228269432625</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_counting_degree_count/images/out_degree_count/0002.png</t>
+          <t>graph/task_graph_counting_degree_count/images/out_degree_count/0024.png</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_counting_degree_count/data/out_degree_count/0002.json</t>
+          <t>graph/task_graph_counting_degree_count/data/out_degree_count/0024.json</t>
         </is>
       </c>
     </row>
@@ -2401,9 +7871,9 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>The image shows a labeled directed graph. Determine the answer: How many nodes have out-degree 3?
+          <t>You are given an image with a labeled directed graph. Question: How many nodes have out-degree 2?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value, sorted in ascending label order.
+Evidence: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
 Answer: set "answer" to the count of matching nodes as an integer.
 Example JSON:
 {"evidence":["B","F"],"answer":2}</t>
@@ -2411,21 +7881,21 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>The image shows a labeled directed graph. Determine the answer: How many nodes have out-degree 3?
+          <t>You are given an image with a labeled directed graph. Question: How many nodes have out-degree 2?
 Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the count of matching nodes as an integer.
+Answer: set "answer" to the count of matching nodes as an integer.
 Example JSON:
 {"answer":2}</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": ["A", "B", "D", "H", "I"], "answer": 5}</t>
+          <t>{"evidence": ["C"], "answer": 1}</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>["A", "B", "D", "H", "I"]</t>
+          <t>["C"]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2439,16 +7909,16 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>8299827996733637</v>
+        <v>1222571224828332</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_counting_degree_count/images/out_degree_count/0000.png</t>
+          <t>graph/task_graph_counting_degree_count/images/out_degree_count/0017.png</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>graph/task_graph_counting_degree_count/data/out_degree_count/0000.json</t>
+          <t>graph/task_graph_counting_degree_count/data/out_degree_count/0017.json</t>
         </is>
       </c>
     </row>
@@ -2465,15 +7935,655 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>The image shows a labeled directed graph. Question: How many nodes have out-degree 4?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["B","F"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled directed graph. Question: How many nodes have out-degree 4?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["C"], "answer": 1}</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>["C"]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1621185748488696</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/out_degree_count/0021.png</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/out_degree_count/0021.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="213.75" customHeight="1">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>out_degree_count</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled directed graph. Question: How many nodes have out-degree 2?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer requirement: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["B","F"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled directed graph. Question: How many nodes have out-degree 2?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [], "answer": 0}</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1759336292711462</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/out_degree_count/0004.png</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/out_degree_count/0004.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="213.75" customHeight="1">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>out_degree_count</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Work from the image with a labeled directed graph. Determine the answer: How many nodes have out-degree 1?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer format: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Work from the image with a labeled directed graph. Determine the answer: How many nodes have out-degree 1?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["1", "6"], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>["1", "6"]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1931465840274954</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/out_degree_count/0000.png</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/out_degree_count/0000.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="213.75" customHeight="1">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>out_degree_count</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Work from the image with a labeled directed graph. Determine the answer: How many nodes have out-degree 0?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer field: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Work from the image with a labeled directed graph. Determine the answer: How many nodes have out-degree 0?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["2", "3", "4", "7", "8"], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>["2", "3", "4", "7", "8"]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1945758746226538</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/out_degree_count/0006.png</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/out_degree_count/0006.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="213.75" customHeight="1">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>out_degree_count</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with a labeled directed graph. Determine the answer: How many nodes have out-degree 2?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer format: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with a labeled directed graph. Determine the answer: How many nodes have out-degree 2?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [], "answer": 0}</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>2064093490086069</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/out_degree_count/0001.png</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/out_degree_count/0001.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="213.75" customHeight="1">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>out_degree_count</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Work from the image with a labeled directed graph. Determine the answer: How many nodes have out-degree 4?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Work from the image with a labeled directed graph. Determine the answer: How many nodes have out-degree 4?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["2", "8"], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>["2", "8"]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>3054053939014602</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/out_degree_count/0014.png</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/out_degree_count/0014.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="213.75" customHeight="1">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>out_degree_count</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Work from the image with a labeled directed graph. Answer this question: How many nodes have out-degree 0?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer rule: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["B","F"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Work from the image with a labeled directed graph. Answer this question: How many nodes have out-degree 0?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["B", "C", "D", "E", "F"], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>["B", "C", "D", "E", "F"]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>4156365690600045</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/out_degree_count/0002.png</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/out_degree_count/0002.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="213.75" customHeight="1">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>out_degree_count</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with a labeled directed graph. Question: How many nodes have out-degree 3?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer rule: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with a labeled directed graph. Question: How many nodes have out-degree 3?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["3", "4", "5"], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>["3", "4", "5"]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>4185713894567162</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/out_degree_count/0012.png</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/out_degree_count/0012.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="213.75" customHeight="1">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>out_degree_count</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled directed graph. Answer this question: How many nodes have out-degree 4?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer format: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["B","F"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled directed graph. Answer this question: How many nodes have out-degree 4?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [], "answer": 0}</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>4311646971207345</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/out_degree_count/0018.png</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/out_degree_count/0018.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="213.75" customHeight="1">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>out_degree_count</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Use the image containing a labeled directed graph. Determine the answer: How many nodes have out-degree 2?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Use the image containing a labeled directed graph. Determine the answer: How many nodes have out-degree 2?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["1", "2", "4", "5"], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>["1", "2", "4", "5"]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>4912520698695886</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/out_degree_count/0009.png</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/out_degree_count/0009.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="213.75" customHeight="1">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>out_degree_count</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>The image shows a labeled directed graph. Task: How many nodes have out-degree 2?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value, sorted in ascending label order.
-Answer requirement: set "answer" to the count of matching nodes as an integer.
+Evidence field: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer field: set "answer" to the count of matching nodes as an integer.
 Example JSON:
 {"evidence":["B","F"],"answer":2}</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>The image shows a labeled directed graph. Task: How many nodes have out-degree 2?
 Return a valid JSON object with key "answer".
@@ -2482,37 +8592,677 @@
 {"answer":2}</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": ["1", "7"], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>["1", "7"]</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["D"], "answer": 1}</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>["D"]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>label_set</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>8862956997050353</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>graph/task_graph_counting_degree_count/images/out_degree_count/0004.png</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>graph/task_graph_counting_degree_count/data/out_degree_count/0004.json</t>
+      <c r="K16" t="n">
+        <v>5003090326352765</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/out_degree_count/0016.png</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/out_degree_count/0016.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="213.75" customHeight="1">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>out_degree_count</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Use the image containing a labeled directed graph. Question: How many nodes have out-degree 2?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer rule: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Use the image containing a labeled directed graph. Question: How many nodes have out-degree 2?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["2", "4", "5", "6", "7"], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>["2", "4", "5", "6", "7"]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>5215609322392307</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/out_degree_count/0011.png</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/out_degree_count/0011.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="213.75" customHeight="1">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>out_degree_count</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled directed graph. How many nodes have out-degree 3?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled directed graph. How many nodes have out-degree 3?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["1", "4", "5", "8"], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>["1", "4", "5", "8"]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>5668017341838112</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/out_degree_count/0022.png</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/out_degree_count/0022.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="213.75" customHeight="1">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>out_degree_count</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled directed graph. How many nodes have out-degree 4?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer requirement: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["B","F"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Look at the image with a labeled directed graph. How many nodes have out-degree 4?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["A", "D"], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>["A", "D"]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>5727358181698577</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/out_degree_count/0010.png</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/out_degree_count/0010.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="213.75" customHeight="1">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>out_degree_count</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Use the image containing a labeled directed graph. Question: How many nodes have out-degree 2?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer requirement: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["B","F"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Use the image containing a labeled directed graph. Question: How many nodes have out-degree 2?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["A", "E"], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>["A", "E"]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>6308318909267954</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/out_degree_count/0007.png</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/out_degree_count/0007.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="213.75" customHeight="1">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>out_degree_count</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled directed graph. Question: How many nodes have out-degree 2?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer rule: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled directed graph. Question: How many nodes have out-degree 2?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["1", "2", "4", "5"], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>["1", "2", "4", "5"]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>6651667367534100</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/out_degree_count/0019.png</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/out_degree_count/0019.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="213.75" customHeight="1">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>out_degree_count</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with a labeled directed graph. Answer this question: How many nodes have out-degree 2?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer format: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["B","F"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with a labeled directed graph. Answer this question: How many nodes have out-degree 2?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [], "answer": 0}</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>7069196874433009</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/out_degree_count/0005.png</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/out_degree_count/0005.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="213.75" customHeight="1">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>out_degree_count</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled directed graph. Determine the answer: How many nodes have out-degree 1?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer format: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["2","7"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled directed graph. Determine the answer: How many nodes have out-degree 1?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["2", "3", "4", "6"], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>["2", "3", "4", "6"]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>7273272538056038</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/out_degree_count/0023.png</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/out_degree_count/0023.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="213.75" customHeight="1">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>out_degree_count</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled directed graph. Task: How many nodes have out-degree 1?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer rule: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["B","F"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a labeled directed graph. Task: How many nodes have out-degree 1?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [], "answer": 0}</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>7629622237339792</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/out_degree_count/0020.png</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/out_degree_count/0020.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="213.75" customHeight="1">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>out_degree_count</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Work from the image with a labeled directed graph. Answer this question: How many nodes have out-degree 1?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer rule: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["B","F"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Work from the image with a labeled directed graph. Answer this question: How many nodes have out-degree 1?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["C", "D", "I"], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>["C", "D", "I"]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>7638403089362116</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/out_degree_count/0013.png</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/out_degree_count/0013.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="213.75" customHeight="1">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>task_graph_counting_degree_count</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>out_degree_count</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with a labeled directed graph. Determine the answer: How many nodes have out-degree 2?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing the labels of all nodes whose asked degree equals the queried value.
+Answer rule: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"evidence":["B","F"],"answer":2}</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>You are given an image with a labeled directed graph. Determine the answer: How many nodes have out-degree 2?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the count of matching nodes as an integer.
+Example JSON:
+{"answer":2}</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": ["A", "B", "E"], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>["A", "B", "E"]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>label_set</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>8525429670009685</v>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/images/out_degree_count/0003.png</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>graph/task_graph_counting_degree_count/data/out_degree_count/0003.json</t>
         </is>
       </c>
     </row>
